--- a/Day1_Excel_Basics.xlsx
+++ b/Day1_Excel_Basics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chjit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F05BDE9-4497-4DBA-8DAA-12B4FA80E03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1842A4-CC45-4BC4-AD66-A5C01E58C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D8C2CD8-A6A8-4999-9E76-E5F64E59EC98}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>Mangos</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Summary</t>
   </si>
 </sst>
 </file>
@@ -122,13 +128,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,10 +450,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E36EDE-D124-4E37-B328-0F8B7F58696C}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,8 +463,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -467,8 +477,12 @@
       <c r="C2" s="3">
         <v>35</v>
       </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v>700</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -478,8 +492,12 @@
       <c r="C3" s="3">
         <v>20</v>
       </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D5" si="0">B3*C3</f>
+        <v>300</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -489,8 +507,12 @@
       <c r="C4" s="3">
         <v>50</v>
       </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -499,6 +521,27 @@
       </c>
       <c r="C5" s="3">
         <v>80</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f>COUNT(B2:B5)</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <f>AVERAGE(C2:C5)</f>
+        <v>46.25</v>
+      </c>
+      <c r="D6">
+        <f>SUM(D2:D5)</f>
+        <v>2460</v>
       </c>
     </row>
   </sheetData>
